--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,314 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -506,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -627,169 +497,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,11 +760,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1107,223 +1087,485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8761904761905" customWidth="1"/>
-    <col min="4" max="5" width="14.1238095238095" customWidth="1"/>
-    <col min="6" max="6" width="9.37142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="9" max="9" width="5.24761904761905" customWidth="1"/>
-    <col min="10" max="10" width="12.1238095238095" customWidth="1"/>
-    <col min="11" max="11" width="15.1238095238095" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.8761904761905" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.1238095238095" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.37142857142857" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5047619047619" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.24761904761905" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.1238095238095" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.1238095238095" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>item.EQuality</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>最差品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>BLUE</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>蓝色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>PURPLE</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>紫色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>最高品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>test.AccessFlag</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>TRUNCATE</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>READ_WRITE</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>WRITE|READ</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>位标记使用示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>roguelike.EEffectType</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AddAttack</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AddDefense</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AddMaxHealth</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AddCritChance</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AddGold</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>roguelike.EEnemyTier</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roguelike.EChoicePool</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1573,6 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -2,14 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,161 +15,117 @@
   <fonts count="21">
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color theme="0"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -185,205 +137,167 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="14">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color auto="1"/>
@@ -397,7 +311,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -412,25 +325,16 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -445,7 +349,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -460,7 +363,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -475,61 +377,42 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -539,26 +422,25 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
@@ -567,7 +449,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -691,7 +573,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -707,59 +589,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Comma" xfId="1"/>
+    <cellStyle name="Currency" xfId="2"/>
+    <cellStyle name="Percent" xfId="3"/>
+    <cellStyle name="Comma [0]" xfId="4"/>
+    <cellStyle name="Currency [0]" xfId="5"/>
+    <cellStyle name="Hyperlink" xfId="6"/>
+    <cellStyle name="Followed Hyperlink" xfId="7"/>
+    <cellStyle name="Note" xfId="8"/>
+    <cellStyle name="Warning Text" xfId="9"/>
+    <cellStyle name="Title" xfId="10"/>
+    <cellStyle name="CExplanatory Text" xfId="11"/>
+    <cellStyle name="Heading 1" xfId="12"/>
+    <cellStyle name="Heading 2" xfId="13"/>
+    <cellStyle name="Heading 3" xfId="14"/>
+    <cellStyle name="Heading 4" xfId="15"/>
+    <cellStyle name="Input" xfId="16"/>
+    <cellStyle name="Output" xfId="17"/>
+    <cellStyle name="Calculation" xfId="18"/>
+    <cellStyle name="Check Cell" xfId="19"/>
+    <cellStyle name="Linked Cell" xfId="20"/>
+    <cellStyle name="Total" xfId="21"/>
+    <cellStyle name="Good" xfId="22"/>
+    <cellStyle name="Bad" xfId="23"/>
+    <cellStyle name="Neutral" xfId="24"/>
+    <cellStyle name="Accent1" xfId="25"/>
+    <cellStyle name="20% - Accent1" xfId="26"/>
+    <cellStyle name="40% - Accent1" xfId="27"/>
+    <cellStyle name="60% - Accent1" xfId="28"/>
+    <cellStyle name="Accent2" xfId="29"/>
+    <cellStyle name="20% - Accent2" xfId="30"/>
+    <cellStyle name="40% - Accent2" xfId="31"/>
+    <cellStyle name="60% - Accent2" xfId="32"/>
+    <cellStyle name="Accent3" xfId="33"/>
+    <cellStyle name="20% - Accent3" xfId="34"/>
+    <cellStyle name="40% - Accent3" xfId="35"/>
+    <cellStyle name="60% - Accent3" xfId="36"/>
+    <cellStyle name="Accent4" xfId="37"/>
+    <cellStyle name="20% - Accent4" xfId="38"/>
+    <cellStyle name="40% - Accent4" xfId="39"/>
+    <cellStyle name="60% - Accent4" xfId="40"/>
+    <cellStyle name="Accent5" xfId="41"/>
+    <cellStyle name="20% - Accent5" xfId="42"/>
+    <cellStyle name="40% - Accent5" xfId="43"/>
+    <cellStyle name="60% - Accent5" xfId="44"/>
+    <cellStyle name="Accent6" xfId="45"/>
+    <cellStyle name="20% - Accent6" xfId="46"/>
+    <cellStyle name="40% - Accent6" xfId="47"/>
+    <cellStyle name="60% - Accent6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -832,7 +716,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -874,74 +758,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -949,80 +773,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1052,22 +827,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1082,7 +857,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1092,18 +866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
-    <col width="20.8761904761905" customWidth="1" style="4" min="3" max="3"/>
-    <col width="14.1238095238095" customWidth="1" style="4" min="4" max="5"/>
-    <col width="9.37142857142857" customWidth="1" style="4" min="6" max="6"/>
+    <col width="20.87619018554688" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.12380981445312" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.371428489685059" customWidth="1" style="4" min="6" max="6"/>
     <col width="5" customWidth="1" style="4" min="7" max="7"/>
-    <col width="13.5047619047619" customWidth="1" style="4" min="8" max="8"/>
-    <col width="5.24761904761905" customWidth="1" style="4" min="9" max="9"/>
-    <col width="12.1238095238095" customWidth="1" style="4" min="10" max="10"/>
-    <col width="15.1238095238095" customWidth="1" style="4" min="11" max="11"/>
+    <col width="13.50476169586182" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.247619152069092" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.12380981445312" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.12380981445312" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1237,342 +1011,554 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>item.EQuality</t>
         </is>
       </c>
-      <c r="C4" s="0" t="b">
+      <c r="C4" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="0" t="b">
+      <c r="D4" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>WHITE</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="0" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>最差品质</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" s="0" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>BLUE</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>蓝</t>
         </is>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="0" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>蓝色的</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" s="0" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>PURPLE</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>紫</t>
         </is>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="0" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>紫色的</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="H7" s="0" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>RED</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>红</t>
         </is>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="0" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>最高品质</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>test.AccessFlag</t>
         </is>
       </c>
-      <c r="C8" s="0" t="b">
+      <c r="C8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="D8" s="0" t="b">
+      <c r="D8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="H9" s="0" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>READ</t>
         </is>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="H10" s="0" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>TRUNCATE</t>
         </is>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="7" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="H11" s="0" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="7" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="H12" s="0" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>READ_WRITE</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>WRITE|READ</t>
         </is>
       </c>
-      <c r="K12" s="0" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>位标记使用示例</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>roguelike.EEffectType</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="K13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>AddAttack</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="K14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>AddDefense</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="K15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="K16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>AddMaxHealth</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>AddCritChance</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>AddGold</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n">
         <v>6</v>
       </c>
+      <c r="K19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>AddPickupRadius</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>AddProjectileDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>AddMoveSpeed</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>roguelike.EEnemyTier</t>
         </is>
       </c>
-      <c r="C20" t="b">
+      <c r="C23" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D20" t="b">
+      <c r="D23" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="K23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="H22" t="inlineStr">
+      <c r="K24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="K25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>roguelike.EChoicePool</t>
         </is>
       </c>
-      <c r="C23" t="b">
+      <c r="C26" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D23" t="b">
+      <c r="D26" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="H24" t="inlineStr">
+      <c r="K26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Rest</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="H25" t="inlineStr">
+      <c r="K27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Treasure</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="K28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="K29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -866,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1369,47 +1369,47 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>roguelike.EEnemyTier</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="b">
-        <v>1</v>
-      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>AddGoldMultiplier</t>
         </is>
       </c>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>roguelike.EEnemyTier</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="n"/>
     </row>
@@ -1423,58 +1423,58 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>roguelike.EChoicePool</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="b">
-        <v>1</v>
-      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>roguelike.EChoicePool</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="n"/>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Treasure</t>
+          <t>Rest</t>
         </is>
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="7" t="n"/>
     </row>
@@ -1507,12 +1507,12 @@
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Treasure</t>
         </is>
       </c>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="7" t="n"/>
     </row>
@@ -1524,9 +1524,15 @@
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
       <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
+      <c r="J30" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="K30" s="7" t="n"/>
     </row>
     <row r="31">
@@ -1555,6 +1561,19 @@
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
